--- a/Dependencies/Takasugi_2024/fragments_per_saap_4barplot_allDS.xlsx
+++ b/Dependencies/Takasugi_2024/fragments_per_saap_4barplot_allDS.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>495</v>
+        <v>590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>840</v>
+        <v>978</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/Dependencies/Takasugi_2024/fragments_per_saap_4barplot_allDS.xlsx
+++ b/Dependencies/Takasugi_2024/fragments_per_saap_4barplot_allDS.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>590</v>
+        <v>768</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -509,7 +509,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>978</v>
+        <v>1181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
